--- a/Data/Ganapathy Residence Material Expense.xlsx
+++ b/Data/Ganapathy Residence Material Expense.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal\Con_java\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/Ganapathy Residence @ VSN Garden/Accounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFDC3B0-49B1-4E19-A760-0FD59A8B2B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="443" documentId="13_ncr:1_{81555393-077D-47DF-B99E-C2CBB59417EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{228CDD79-79C8-4FD1-BD1D-2DBBC4B23747}"/>
   <bookViews>
-    <workbookView xWindow="36300" yWindow="1950" windowWidth="21600" windowHeight="11235" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Details" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="59">
   <si>
     <t>DATE</t>
   </si>
@@ -225,9 +225,6 @@
     <t>TOTAL AMOUNT</t>
   </si>
   <si>
-    <t>PALANU MURUGAN</t>
-  </si>
-  <si>
     <t>ACC</t>
   </si>
   <si>
@@ -241,6 +238,9 @@
   </si>
   <si>
     <t>PAINTING</t>
+  </si>
+  <si>
+    <t>Pending Amount</t>
   </si>
 </sst>
 </file>
@@ -270,21 +270,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -403,22 +397,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -448,12 +431,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -672,6 +650,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -957,19 +939,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="25.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="25.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.90625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -995,7 +977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="10">
         <v>46050</v>
       </c>
@@ -1022,7 +1004,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>46053</v>
       </c>
@@ -1047,7 +1029,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>46053</v>
       </c>
@@ -1072,7 +1054,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>46053</v>
       </c>
@@ -1096,7 +1078,7 @@
         <v>63500</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>46054</v>
       </c>
@@ -1123,7 +1105,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>46070</v>
       </c>
@@ -1147,12 +1129,12 @@
         <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
         <v>10500</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="21">
         <f>SUM(H9,H5,H14,H19)</f>
         <v>233740</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>46071</v>
       </c>
@@ -1179,7 +1161,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>46088</v>
       </c>
@@ -1201,7 +1183,7 @@
         <v>85010</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>46088</v>
       </c>
@@ -1219,7 +1201,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>46093</v>
       </c>
@@ -1244,7 +1226,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>46093</v>
       </c>
@@ -1269,7 +1251,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>46093</v>
       </c>
@@ -1296,7 +1278,7 @@
         <v>16200</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>46108</v>
       </c>
@@ -1318,7 +1300,7 @@
         <v>26650</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>46113</v>
       </c>
@@ -1343,7 +1325,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>46113</v>
       </c>
@@ -1368,7 +1350,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>46113</v>
       </c>
@@ -1395,7 +1377,7 @@
         <v>4275</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>46114</v>
       </c>
@@ -1422,7 +1404,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>46120</v>
       </c>
@@ -1446,7 +1428,7 @@
         <v>58580</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>46126</v>
       </c>
@@ -1471,7 +1453,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>46126</v>
       </c>
@@ -1496,7 +1478,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>46125</v>
       </c>
@@ -1514,7 +1496,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>46125</v>
       </c>
@@ -1541,7 +1523,7 @@
         <v>9275</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="17">
         <v>46131</v>
       </c>
@@ -1566,7 +1548,7 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>46137</v>
       </c>
@@ -1582,7 +1564,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>46142</v>
       </c>
@@ -1609,7 +1591,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>46150</v>
       </c>
@@ -1627,12 +1609,12 @@
         <v>10650</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>46150</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18" t="s">
@@ -1645,33 +1627,59 @@
         <v>10755</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="18"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="10">
+        <v>46172</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>30</v>
+      </c>
       <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="19"/>
+      <c r="D29" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="18">
+        <v>2</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="19">
+        <v>6000</v>
+      </c>
       <c r="H29" s="11">
         <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="19"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="17">
+        <v>46172</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="18">
+        <v>50</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="19">
+        <v>290</v>
+      </c>
       <c r="H30" s="20">
         <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1684,7 +1692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="17"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -1697,7 +1705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="17"/>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
@@ -1710,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="17"/>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -1723,7 +1731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1736,7 +1744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="17"/>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -1749,19 +1757,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41"/>
     </row>
   </sheetData>
@@ -1787,14 +1795,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7945D8E7-2C2E-4C89-B38E-C74186D29A9E}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1805,7 +1813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
@@ -1816,7 +1824,7 @@
         <v>5125</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
@@ -1827,7 +1835,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -1838,7 +1846,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
@@ -1849,7 +1857,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
@@ -1860,7 +1868,7 @@
         <v>5950</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
@@ -1871,7 +1879,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
@@ -1880,7 +1888,7 @@
       </c>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
@@ -1889,15 +1897,15 @@
       </c>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1905,15 +1913,21 @@
       </c>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>58</v>
-      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1923,14 +1937,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC52B97-F8EC-489B-AAAD-008E3D44EA2D}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -1944,7 +1958,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="str" cm="1">
         <f t="array" ref="A2:A10">_xlfn.UNIQUE('Material Details'!B2:B1008)</f>
         <v>BRICK</v>
@@ -1961,7 +1975,7 @@
         <v>144000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="str">
         <v>M-SAND</v>
       </c>
@@ -1977,7 +1991,7 @@
         <v>52500</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="str">
         <v>20 MM JALLY</v>
       </c>
@@ -1993,7 +2007,7 @@
         <v>38000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="str">
         <v>STEEL</v>
       </c>
@@ -2009,23 +2023,23 @@
         <v>233740</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="str">
         <v>CEMENT</v>
       </c>
       <c r="B6" s="6">
         <f>SUMIF('Material Details'!B6:B1012,A6,'Material Details'!E6:E1012)</f>
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="7">
         <f>SUMIF('Material Details'!B6:B1012,A6,'Material Details'!H6:H1012)</f>
-        <v>30770</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="str">
         <v>ELECTRICAL</v>
       </c>
@@ -2041,28 +2055,39 @@
         <v>15929</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="str">
         <v>P-SAND</v>
       </c>
       <c r="B8" s="6">
         <f>SUMIF('Material Details'!B11:B1014,A8,'Material Details'!E11:E1014)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="7">
         <f>SUMIF('Material Details'!B8:B1014,A8,'Material Details'!H8:H1014)</f>
-        <v>23000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <v>PLUMBING</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="6">
+        <f>SUMIF('Material Details'!B12:B1015,A9,'Material Details'!E12:E1015)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="7">
+        <f>SUMIF('Material Details'!B9:B1015,A9,'Material Details'!H9:H1015)</f>
+        <v>10755</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0</v>
       </c>
@@ -2074,16 +2099,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96697B0-05D6-4BCA-A61B-0D246D1FF2DE}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -2097,7 +2122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="str" cm="1">
         <f t="array" ref="A2:A9">_xlfn.UNIQUE('Material Details'!D2:D1008)</f>
         <v>VEL BRICK</v>
@@ -2115,24 +2140,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="str">
         <v>RSK</v>
       </c>
       <c r="B3" s="7">
         <f>SUMIF('Material Details'!D2:D1008,A3,'Material Details'!H2:H1008)</f>
-        <v>113500</v>
+        <v>125500</v>
       </c>
       <c r="C3" s="7">
         <f>SUMIF('Payment Details'!B2:B992,'Vendor Balance Sheet'!A3,'Payment Details'!C2:C992)</f>
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D6" si="0">B3-C3</f>
-        <v>13500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="str">
         <v>AK STEELS</v>
       </c>
@@ -2149,7 +2174,7 @@
         <v>3740</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="str">
         <v>LOCAL</v>
       </c>
@@ -2166,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="str">
         <v>RAMDEV HARDWARES</v>
       </c>
@@ -2176,14 +2201,14 @@
       </c>
       <c r="C6" s="7">
         <f>SUMIF('Payment Details'!B3:B993,'Vendor Balance Sheet'!A6,'Payment Details'!C3:C993)</f>
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>24308</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="str">
         <v>PALANI MURUGAN</v>
       </c>
@@ -2193,43 +2218,33 @@
       </c>
       <c r="C7" s="7">
         <f>SUMIF('Payment Details'!B4:B994,'Vendor Balance Sheet'!A7,'Payment Details'!C4:C994)</f>
-        <v>0</v>
+        <v>20225</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" ref="D7" si="1">B7-C7</f>
-        <v>20475</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="str">
         <v>CHAKRA TRADERS</v>
       </c>
       <c r="B8" s="7">
         <f>SUMIF('Material Details'!D7:D1013,A8,'Material Details'!H7:H1013)</f>
-        <v>9275</v>
+        <v>23775</v>
       </c>
       <c r="C8" s="7">
         <f>SUMIF('Payment Details'!B5:B995,'Vendor Balance Sheet'!A8,'Payment Details'!C5:C995)</f>
-        <v>9275</v>
+        <v>23775</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" ref="D8" si="2">B8-C8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="4">
-        <v>16200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="4">
-        <v>4275</v>
       </c>
     </row>
   </sheetData>
@@ -2240,17 +2255,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B843CC5F-739E-45E9-AC65-8442CF552E38}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="3"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2270,7 +2285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>46050</v>
       </c>
@@ -2290,7 +2305,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>46057</v>
       </c>
@@ -2310,7 +2325,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>46074</v>
       </c>
@@ -2330,7 +2345,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>46088</v>
       </c>
@@ -2350,7 +2365,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>46102</v>
       </c>
@@ -2370,7 +2385,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>46109</v>
       </c>
@@ -2390,7 +2405,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>46116</v>
       </c>
@@ -2410,7 +2425,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>46123</v>
       </c>
@@ -2430,7 +2445,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>46125</v>
       </c>
@@ -2450,27 +2465,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
         <v>46144</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="25">
-        <v>20000</v>
-      </c>
-      <c r="D11" s="25" t="s">
+      <c r="E11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>46144</v>
       </c>
@@ -2487,10 +2502,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>46151</v>
       </c>
@@ -2510,39 +2525,87 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="7">
+        <v>225</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>46172</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="7">
+        <v>25000</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
+        <v>46172</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="7">
+        <v>14500</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>46172</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
@@ -2550,7 +2613,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
@@ -2558,7 +2621,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
@@ -2566,7 +2629,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
@@ -2574,7 +2637,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
@@ -2582,7 +2645,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
